--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,28 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>16.4691</v>
+        <v>16.60984</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63189</v>
+        <v>16.41052</v>
       </c>
       <c r="E2" t="n">
-        <v>16.40058</v>
+        <v>16.5455</v>
       </c>
       <c r="F2" t="n">
-        <v>42.37083</v>
+        <v>42.16421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05056</v>
+        <v>0.05147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81581</v>
+        <v>1.81203</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.58231</v>
+        <v>16.58789</v>
       </c>
       <c r="D3" t="n">
-        <v>16.09568</v>
+        <v>16.51543</v>
       </c>
       <c r="E3" t="n">
-        <v>16.99296</v>
+        <v>16.52254</v>
       </c>
       <c r="F3" t="n">
-        <v>42.672</v>
+        <v>42.54877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05037</v>
+        <v>0.05067</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79395</v>
+        <v>1.82344</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.74671</v>
+        <v>16.84302</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61203</v>
+        <v>16.54838</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42513</v>
+        <v>16.67594</v>
       </c>
       <c r="F4" t="n">
-        <v>41.84899</v>
+        <v>41.28075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05074</v>
+        <v>0.0497</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80852</v>
+        <v>1.80353</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.74201</v>
+        <v>16.66396</v>
       </c>
       <c r="D5" t="n">
-        <v>16.01422</v>
+        <v>16.50089</v>
       </c>
       <c r="E5" t="n">
-        <v>16.55054</v>
+        <v>16.6085</v>
       </c>
       <c r="F5" t="n">
-        <v>41.03205</v>
+        <v>42.66479</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05083</v>
+        <v>0.05025</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82242</v>
+        <v>1.80834</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.84575</v>
+        <v>17.05378</v>
       </c>
       <c r="D6" t="n">
-        <v>16.75062</v>
+        <v>16.26026</v>
       </c>
       <c r="E6" t="n">
-        <v>16.65264</v>
+        <v>16.90552</v>
       </c>
       <c r="F6" t="n">
-        <v>42.32451</v>
+        <v>41.94637</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05038</v>
+        <v>0.05107</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83039</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.01121</v>
+        <v>16.8814</v>
       </c>
       <c r="D7" t="n">
-        <v>16.43591</v>
+        <v>16.4588</v>
       </c>
       <c r="E7" t="n">
-        <v>16.77754</v>
+        <v>16.64857</v>
       </c>
       <c r="F7" t="n">
-        <v>41.78166</v>
+        <v>42.13843</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0499</v>
+        <v>0.05009</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83167</v>
+        <v>1.81977</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.59167</v>
+        <v>16.75808</v>
       </c>
       <c r="D8" t="n">
-        <v>16.40438</v>
+        <v>16.49984</v>
       </c>
       <c r="E8" t="n">
-        <v>16.69092</v>
+        <v>16.59385</v>
       </c>
       <c r="F8" t="n">
-        <v>41.72766</v>
+        <v>42.22896</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05055</v>
+        <v>0.05011</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80803</v>
+        <v>1.82842</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.38653</v>
+        <v>16.39334</v>
       </c>
       <c r="D9" t="n">
-        <v>16.63403</v>
+        <v>16.31268</v>
       </c>
       <c r="E9" t="n">
-        <v>16.39682</v>
+        <v>16.34655</v>
       </c>
       <c r="F9" t="n">
-        <v>42.64991</v>
+        <v>41.624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05021</v>
+        <v>0.05012</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83523</v>
+        <v>1.81035</v>
       </c>
     </row>
     <row r="10">
@@ -660,386 +655,284 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.80694</v>
+        <v>16.82081</v>
       </c>
       <c r="D10" t="n">
-        <v>16.22526</v>
+        <v>16.09331</v>
       </c>
       <c r="E10" t="n">
-        <v>16.54269</v>
+        <v>16.57671</v>
       </c>
       <c r="F10" t="n">
-        <v>42.52254</v>
+        <v>41.43148</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04956</v>
+        <v>0.04916</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84561</v>
+        <v>1.81844</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.76114</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.48346</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.62162</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41.50954</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05079</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.84008</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.45081</v>
+        <v>16.68301</v>
       </c>
       <c r="D12" t="n">
-        <v>16.62492</v>
+        <v>16.30633</v>
       </c>
       <c r="E12" t="n">
-        <v>16.58185</v>
+        <v>16.59794</v>
       </c>
       <c r="F12" t="n">
-        <v>42.50168</v>
+        <v>42.66971</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04929</v>
+        <v>0.05079</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84543</v>
+        <v>1.81618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.64045</v>
+        <v>16.78173</v>
       </c>
       <c r="D13" t="n">
-        <v>16.76025</v>
+        <v>16.35389</v>
       </c>
       <c r="E13" t="n">
-        <v>16.49078</v>
+        <v>16.63914</v>
       </c>
       <c r="F13" t="n">
-        <v>42.77689</v>
+        <v>41.77788</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05077</v>
+        <v>0.05143</v>
       </c>
       <c r="H13" t="n">
-        <v>1.74556</v>
+        <v>1.79104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.89571</v>
+        <v>16.76791</v>
       </c>
       <c r="D14" t="n">
-        <v>16.51303</v>
+        <v>15.86454</v>
       </c>
       <c r="E14" t="n">
-        <v>16.85514</v>
+        <v>16.64932</v>
       </c>
       <c r="F14" t="n">
-        <v>42.4618</v>
+        <v>42.07016</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05052</v>
+        <v>0.05119</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8274</v>
+        <v>1.82042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.77546</v>
+        <v>16.78534</v>
       </c>
       <c r="D15" t="n">
-        <v>16.26762</v>
+        <v>16.05941</v>
       </c>
       <c r="E15" t="n">
-        <v>16.79725</v>
+        <v>16.75844</v>
       </c>
       <c r="F15" t="n">
-        <v>42.74284</v>
+        <v>41.82481</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05011</v>
+        <v>0.05003</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83329</v>
+        <v>1.79264</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.4922</v>
+        <v>17.05144</v>
       </c>
       <c r="D16" t="n">
-        <v>16.57014</v>
+        <v>16.51732</v>
       </c>
       <c r="E16" t="n">
-        <v>16.9056</v>
+        <v>16.59704</v>
       </c>
       <c r="F16" t="n">
-        <v>42.74557</v>
+        <v>42.99681</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05022</v>
+        <v>0.05166</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81563</v>
+        <v>1.84549</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.08681</v>
+        <v>17.16177</v>
       </c>
       <c r="D17" t="n">
-        <v>16.74018</v>
+        <v>16.34723</v>
       </c>
       <c r="E17" t="n">
-        <v>16.45564</v>
+        <v>16.65621</v>
       </c>
       <c r="F17" t="n">
-        <v>42.54471</v>
+        <v>42.52051</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05021</v>
+        <v>0.04989</v>
       </c>
       <c r="H17" t="n">
-        <v>1.80542</v>
+        <v>1.80359</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.73368</v>
+        <v>16.75661</v>
       </c>
       <c r="D18" t="n">
-        <v>16.47488</v>
+        <v>16.37537</v>
       </c>
       <c r="E18" t="n">
-        <v>16.20637</v>
+        <v>16.44683</v>
       </c>
       <c r="F18" t="n">
-        <v>41.74186</v>
+        <v>42.28946</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05062</v>
+        <v>0.05051</v>
       </c>
       <c r="H18" t="n">
-        <v>1.80952</v>
+        <v>1.79704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16.91487</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.37914</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.39186</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.18327</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.77867</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.52918</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.6322</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.44183</v>
-      </c>
-      <c r="F19" t="n">
-        <v>41.98501</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05071</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.81669</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60661</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.1229</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.60316</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.12302</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.62061</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.09561</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.59665</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.13075</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.60817</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.10636</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.60904</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.11229</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.61127</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.07366</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.61238</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.11608</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.61026</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.10691</v>
+      <c r="C20" t="n">
+        <v>17.05089</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.3095</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.44435</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.10952</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81454</v>
       </c>
     </row>
   </sheetData>
